--- a/5/search/FY5_Missile2_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY5_Missile2_results/fine_tuned/comparison.xlsx
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="C3" t="n">
-        <v>133.9</v>
+        <v>138.4</v>
       </c>
       <c r="D3" t="n">
         <v>19.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
         <v>3.600000000000001</v>
